--- a/data/merged/2026-08-31/MERGED_IT_Mite-Vacuum_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_IT_Mite-Vacuum_2026-08-31.xlsx
@@ -3689,13 +3689,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3821,13 +3821,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3997,13 +3997,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4085,13 +4085,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4152,94 +4152,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId33" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Product 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId34" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Product 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId35" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4581,7 +4493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR36"/>
+  <dimension ref="A1:BR34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -7484,7 +7396,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -7497,23 +7409,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO Galleggiante per Lavasciuga Pavimenti Filtro per Serbatoio di Scarico Acciaio Inossidabile Parte Accessori Facile In</t>
+          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F8W81X7Y?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M20" s="14"/>
@@ -7533,9 +7445,13 @@
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20" s="2"/>
-      <c r="AD20" s="19"/>
+      <c r="AD20" s="19">
+        <v>2</v>
+      </c>
       <c r="AE20" s="15"/>
-      <c r="AF20" s="21"/>
+      <c r="AF20" s="21">
+        <v>2.5</v>
+      </c>
       <c r="AG20" s="22">
         <v>0</v>
       </c>
@@ -7586,7 +7502,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -7599,23 +7515,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allerge</t>
+          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="M21" s="14"/>
@@ -7636,11 +7552,11 @@
       <c r="AB21"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AE21" s="15"/>
       <c r="AF21" s="21">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -7692,7 +7608,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -7705,23 +7621,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspiratore Floreale Delight (Plant Essential Oil)</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="M22" s="14"/>
@@ -7742,11 +7658,11 @@
       <c r="AB22"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE22" s="15"/>
       <c r="AF22" s="21">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -7798,7 +7714,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -7811,23 +7727,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con conte</t>
+          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M23" s="14"/>
@@ -7848,11 +7764,11 @@
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE23" s="15"/>
       <c r="AF23" s="21">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -7904,7 +7820,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -7917,23 +7833,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="M24" s="14"/>
@@ -7954,11 +7870,11 @@
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AE24" s="15"/>
       <c r="AF24" s="21">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -8010,7 +7926,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8023,23 +7939,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Dis</t>
+          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="M25" s="14"/>
@@ -8060,11 +7976,11 @@
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AE25" s="15"/>
       <c r="AF25" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8116,7 +8032,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8129,23 +8045,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per let</t>
+          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="M26" s="14"/>
@@ -8166,11 +8082,11 @@
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="AE26" s="15"/>
       <c r="AF26" s="21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8222,7 +8138,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8235,23 +8151,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento R</t>
+          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="M27" s="14"/>
@@ -8272,11 +8188,11 @@
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="19">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE27" s="15"/>
       <c r="AF27" s="21">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -8328,7 +8244,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -8341,23 +8257,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a</t>
+          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M28" s="14"/>
@@ -8378,11 +8294,11 @@
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -8434,7 +8350,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GHQLQBYD</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -8447,23 +8363,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa o</t>
+          <t>Aspirapolvere per Materassi,Aspira Materasso Antiacaro con Una Forte Potenza di Aspirazione, Aspira Acari per Materassi e Div</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GHQLQBYD?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GHQLQBYD</t>
         </is>
       </c>
       <c r="M29" s="14"/>
@@ -8484,11 +8400,11 @@
       <c r="AB29"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AE29" s="15"/>
       <c r="AF29" s="21">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -8540,7 +8456,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -8553,23 +8469,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="M30" s="14"/>
@@ -8590,11 +8506,11 @@
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="AE30" s="15"/>
       <c r="AF30" s="21">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -8646,7 +8562,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0GHQLQBYD</t>
+          <t>B0GSZ8XVY3</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -8659,23 +8575,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere per Materassi,Aspira Materasso Antiacaro con Una Forte Potenza di Aspirazione, Aspira Acari per Materassi e Div</t>
+          <t>Lubluelu Aspirapolvere Antiacari 3-in-1 per Materassi, Potente Aspirazione 18 kPa, Pulitore per Materassi contro Acari, Polve</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GHQLQBYD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GSZ8XVY3?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0GHQLQBYD</t>
+          <t>B0GSZ8XVY3</t>
         </is>
       </c>
       <c r="M31" s="14"/>
@@ -8696,11 +8612,11 @@
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE31" s="15"/>
       <c r="AF31" s="21">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -8752,7 +8668,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -8765,23 +8681,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, As</t>
+          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-Cs12.000 colpi/min, potenza 600 W, contenito</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="M32" s="14"/>
@@ -8801,13 +8717,9 @@
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
-      <c r="AD32" s="19">
-        <v>28</v>
-      </c>
+      <c r="AD32" s="19"/>
       <c r="AE32" s="15"/>
-      <c r="AF32" s="21">
-        <v>3.6</v>
-      </c>
+      <c r="AF32" s="21"/>
       <c r="AG32" s="22">
         <v>0</v>
       </c>
@@ -8858,7 +8770,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GSZ8XVY3</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -8871,23 +8783,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirapolvere Antiacari 3-in-1 per Materassi, Potente Aspirazione 18 kPa, Pulitore per Materassi contro Acari, Polve</t>
+          <t>JIGOO T600 Aspiratore acaro per materassi, 700 W aspirapolvere acari con luce UV, 15 kpa attrazione acari aspirapolvere antia</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GSZ8XVY3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GWD94VPC?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GSZ8XVY3</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="M33" s="14"/>
@@ -8903,12 +8815,14 @@
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
       <c r="Y33" s="19"/>
-      <c r="Z33" s="20"/>
+      <c r="Z33" s="20">
+        <v>125.35</v>
+      </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="19">
-        <v>7</v>
+        <v>801</v>
       </c>
       <c r="AE33" s="15"/>
       <c r="AF33" s="21">
@@ -8964,7 +8878,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0H5K5QQZC</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -8977,23 +8891,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-Cs12.000 colpi/min, potenza 600 W, contenito</t>
+          <t>VIHBRAI Aspirapolvere senza fili per acari per materassi, con luce UV-C e potenza di aspirazione da 10 kPa, doppio contenitor</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H5K5QQZC?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0H5K5QQZC</t>
         </is>
       </c>
       <c r="M34" s="14"/>
@@ -9013,9 +8927,13 @@
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
-      <c r="AD34" s="19"/>
+      <c r="AD34" s="19">
+        <v>2</v>
+      </c>
       <c r="AE34" s="15"/>
-      <c r="AF34" s="21"/>
+      <c r="AF34" s="21">
+        <v>4</v>
+      </c>
       <c r="AG34" s="22">
         <v>0</v>
       </c>
@@ -9058,220 +8976,6 @@
       <c r="BP34" s="23"/>
       <c r="BQ34" s="23"/>
       <c r="BR34" s="13"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
-        <v>34</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>B0GWD94VPC</t>
-        </is>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO T600 Aspiratore acaro per materassi, 700 W aspirapolvere acari con luce UV, 15 kpa attrazione acari aspirapolvere antia</t>
-        </is>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0GWD94VPC?psc=1</t>
-        </is>
-      </c>
-      <c r="K35" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L35" s="14" t="inlineStr">
-        <is>
-          <t>B0GWD94VPC</t>
-        </is>
-      </c>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="20">
-        <v>125.35</v>
-      </c>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35" s="2"/>
-      <c r="AD35" s="19">
-        <v>801</v>
-      </c>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="20"/>
-      <c r="AI35" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ35"/>
-      <c r="AK35" s="13"/>
-      <c r="AL35" s="19"/>
-      <c r="AM35" s="13"/>
-      <c r="AN35" s="13"/>
-      <c r="AO35" s="13"/>
-      <c r="AP35"/>
-      <c r="AQ35" s="19"/>
-      <c r="AR35" s="19"/>
-      <c r="AS35" s="14"/>
-      <c r="AT35" s="13"/>
-      <c r="AU35" s="13"/>
-      <c r="AV35" s="14"/>
-      <c r="AW35" s="13"/>
-      <c r="AX35" s="13"/>
-      <c r="AY35" s="13"/>
-      <c r="AZ35" s="13"/>
-      <c r="BA35" s="13"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="13"/>
-      <c r="BD35" s="13"/>
-      <c r="BE35" s="13"/>
-      <c r="BF35" s="13"/>
-      <c r="BG35" s="13"/>
-      <c r="BH35" s="14"/>
-      <c r="BI35" s="23"/>
-      <c r="BJ35" s="23"/>
-      <c r="BK35" s="23"/>
-      <c r="BL35" s="23"/>
-      <c r="BM35" s="23"/>
-      <c r="BN35" s="23"/>
-      <c r="BO35" s="23"/>
-      <c r="BP35" s="23"/>
-      <c r="BQ35" s="23"/>
-      <c r="BR35" s="13"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>B0H5K5QQZC</t>
-        </is>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>VIHBRAI Aspirapolvere senza fili per acari per materassi, con luce UV-C e potenza di aspirazione da 10 kPa, doppio contenitor</t>
-        </is>
-      </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H5K5QQZC?psc=1</t>
-        </is>
-      </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L36" s="14" t="inlineStr">
-        <is>
-          <t>B0H5K5QQZC</t>
-        </is>
-      </c>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="19"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36"/>
-      <c r="AB36"/>
-      <c r="AC36" s="2"/>
-      <c r="AD36" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="21">
-        <v>4</v>
-      </c>
-      <c r="AG36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="20"/>
-      <c r="AI36" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ36"/>
-      <c r="AK36" s="13"/>
-      <c r="AL36" s="19"/>
-      <c r="AM36" s="13"/>
-      <c r="AN36" s="13"/>
-      <c r="AO36" s="13"/>
-      <c r="AP36"/>
-      <c r="AQ36" s="19"/>
-      <c r="AR36" s="19"/>
-      <c r="AS36" s="14"/>
-      <c r="AT36" s="13"/>
-      <c r="AU36" s="13"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="13"/>
-      <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
-      <c r="AZ36" s="13"/>
-      <c r="BA36" s="13"/>
-      <c r="BB36" s="13"/>
-      <c r="BC36" s="13"/>
-      <c r="BD36" s="13"/>
-      <c r="BE36" s="13"/>
-      <c r="BF36" s="13"/>
-      <c r="BG36" s="13"/>
-      <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
-      <c r="BJ36" s="23"/>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="23"/>
-      <c r="BM36" s="23"/>
-      <c r="BN36" s="23"/>
-      <c r="BO36" s="23"/>
-      <c r="BP36" s="23"/>
-      <c r="BQ36" s="23"/>
-      <c r="BR36" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9381,93 +9085,83 @@
     <hyperlink ref="J19" r:id="rId102" tooltip="https://www.amazon.it/dp/B0F8HD3649?psc=1"/>
     <hyperlink ref="K19" r:id="rId103" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CtAiuTm1L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L19" r:id="rId104" tooltip="https://www.amazon.it/dp/B0F8HD3649"/>
-    <hyperlink ref="C20" r:id="rId105" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
+    <hyperlink ref="C20" r:id="rId105" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
     <hyperlink ref="G20" r:id="rId106" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J20" r:id="rId107" tooltip="https://www.amazon.it/dp/B0F8W81X7Y?psc=1"/>
-    <hyperlink ref="K20" r:id="rId108" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7132zWnxJ5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId109" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
-    <hyperlink ref="C21" r:id="rId110" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="J20" r:id="rId107" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K20" r:id="rId108" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId109" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="C21" r:id="rId110" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
     <hyperlink ref="G21" r:id="rId111" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J21" r:id="rId112" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K21" r:id="rId113" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId114" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C22" r:id="rId115" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
+    <hyperlink ref="J21" r:id="rId112" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K21" r:id="rId113" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId114" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="C22" r:id="rId115" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
     <hyperlink ref="G22" r:id="rId116" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J22" r:id="rId117" tooltip="https://www.amazon.it/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K22" r:id="rId118" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId119" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="C23" r:id="rId120" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="J22" r:id="rId117" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
+    <hyperlink ref="K22" r:id="rId118" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId119" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="C23" r:id="rId120" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
     <hyperlink ref="G23" r:id="rId121" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J23" r:id="rId122" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K23" r:id="rId123" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId124" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="C24" r:id="rId125" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="J23" r:id="rId122" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K23" r:id="rId123" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId124" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="C24" r:id="rId125" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
     <hyperlink ref="G24" r:id="rId126" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J24" r:id="rId127" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
-    <hyperlink ref="K24" r:id="rId128" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511XZVAimmL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId129" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="C25" r:id="rId130" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="J24" r:id="rId127" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
+    <hyperlink ref="K24" r:id="rId128" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId129" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="C25" r:id="rId130" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
     <hyperlink ref="G25" r:id="rId131" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J25" r:id="rId132" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K25" r:id="rId133" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gt+j80L3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId134" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
-    <hyperlink ref="C26" r:id="rId135" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="J25" r:id="rId132" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
+    <hyperlink ref="K25" r:id="rId133" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId134" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="C26" r:id="rId135" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
     <hyperlink ref="G26" r:id="rId136" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J26" r:id="rId137" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
-    <hyperlink ref="K26" r:id="rId138" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41qFOExg5PL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId139" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
-    <hyperlink ref="C27" r:id="rId140" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="J26" r:id="rId137" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
+    <hyperlink ref="K26" r:id="rId138" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId139" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="C27" r:id="rId140" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
     <hyperlink ref="G27" r:id="rId141" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J27" r:id="rId142" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
-    <hyperlink ref="K27" r:id="rId143" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61mGX4QmLkL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId144" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
-    <hyperlink ref="C28" r:id="rId145" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="J27" r:id="rId142" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
+    <hyperlink ref="K27" r:id="rId143" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId144" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="C28" r:id="rId145" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
     <hyperlink ref="G28" r:id="rId146" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J28" r:id="rId147" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
-    <hyperlink ref="K28" r:id="rId148" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71yKveOz1uL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId149" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
-    <hyperlink ref="C29" r:id="rId150" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="J28" r:id="rId147" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K28" r:id="rId148" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId149" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="C29" r:id="rId150" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
     <hyperlink ref="G29" r:id="rId151" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J29" r:id="rId152" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
-    <hyperlink ref="K29" r:id="rId153" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61R1ViIQaTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId154" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
-    <hyperlink ref="C30" r:id="rId155" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="J29" r:id="rId152" tooltip="https://www.amazon.it/dp/B0GHQLQBYD?psc=1"/>
+    <hyperlink ref="K29" r:id="rId153" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId154" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
+    <hyperlink ref="C30" r:id="rId155" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
     <hyperlink ref="G30" r:id="rId156" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J30" r:id="rId157" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K30" r:id="rId158" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId159" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="C31" r:id="rId160" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
+    <hyperlink ref="J30" r:id="rId157" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
+    <hyperlink ref="K30" r:id="rId158" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId159" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="C31" r:id="rId160" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
     <hyperlink ref="G31" r:id="rId161" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J31" r:id="rId162" tooltip="https://www.amazon.it/dp/B0GHQLQBYD?psc=1"/>
-    <hyperlink ref="K31" r:id="rId163" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610gU-iwIJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId164" tooltip="https://www.amazon.it/dp/B0GHQLQBYD"/>
-    <hyperlink ref="C32" r:id="rId165" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="J31" r:id="rId162" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3?psc=1"/>
+    <hyperlink ref="K31" r:id="rId163" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId164" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
+    <hyperlink ref="C32" r:id="rId165" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
     <hyperlink ref="G32" r:id="rId166" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J32" r:id="rId167" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
-    <hyperlink ref="K32" r:id="rId168" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51lAD9Ta2TL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId169" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
-    <hyperlink ref="C33" r:id="rId170" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
+    <hyperlink ref="J32" r:id="rId167" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K32" r:id="rId168" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId169" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="C33" r:id="rId170" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
     <hyperlink ref="G33" r:id="rId171" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J33" r:id="rId172" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3?psc=1"/>
-    <hyperlink ref="K33" r:id="rId173" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId174" tooltip="https://www.amazon.it/dp/B0GSZ8XVY3"/>
-    <hyperlink ref="C34" r:id="rId175" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="J33" r:id="rId172" tooltip="https://www.amazon.it/dp/B0GWD94VPC?psc=1"/>
+    <hyperlink ref="K33" r:id="rId173" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId174" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
+    <hyperlink ref="C34" r:id="rId175" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
     <hyperlink ref="G34" r:id="rId176" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J34" r:id="rId177" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K34" r:id="rId178" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId179" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
-    <hyperlink ref="C35" r:id="rId180" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
-    <hyperlink ref="G35" r:id="rId181" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J35" r:id="rId182" tooltip="https://www.amazon.it/dp/B0GWD94VPC?psc=1"/>
-    <hyperlink ref="K35" r:id="rId183" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId184" tooltip="https://www.amazon.it/dp/B0GWD94VPC"/>
-    <hyperlink ref="C36" r:id="rId185" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
-    <hyperlink ref="G36" r:id="rId186" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J36" r:id="rId187" tooltip="https://www.amazon.it/dp/B0H5K5QQZC?psc=1"/>
-    <hyperlink ref="K36" r:id="rId188" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId189" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
+    <hyperlink ref="J34" r:id="rId177" tooltip="https://www.amazon.it/dp/B0H5K5QQZC?psc=1"/>
+    <hyperlink ref="K34" r:id="rId178" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61H5ky-wD0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId179" tooltip="https://www.amazon.it/dp/B0H5K5QQZC"/>
   </hyperlinks>
-  <drawing r:id="rId190"/>
+  <drawing r:id="rId180"/>
 </worksheet>
 </file>
 
